--- a/no-basis/CurrentBuild/ValueSet-no-basis-location-type.valueset.xlsx
+++ b/no-basis/CurrentBuild/ValueSet-no-basis-location-type.valueset.xlsx
@@ -7,15 +7,15 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include from no-basis-locatio" r:id="rId4" sheetId="2"/>
-    <sheet name="Include from RoleCode" r:id="rId5" sheetId="3"/>
-    <sheet name="Exclude from RoleCode" r:id="rId6" sheetId="4"/>
+    <sheet name="Include #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Include #1" r:id="rId5" sheetId="3"/>
+    <sheet name="Exclude #2" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="36">
   <si>
     <t>Property</t>
   </si>
@@ -66,9 +66,6 @@
   </si>
   <si>
     <t>Publisher</t>
-  </si>
-  <si>
-    <t>HL7 Norway</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -334,44 +331,42 @@
       <c r="A9" t="s" s="2">
         <v>16</v>
       </c>
-      <c r="B9" t="s" s="2">
-        <v>17</v>
-      </c>
+      <c r="B9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s" s="2">
         <v>18</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>20</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="B14" t="s" s="2">
         <v>24</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -390,28 +385,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="B4" t="s" s="2">
         <v>29</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -433,7 +428,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C1" t="s" s="1">
         <v>1</v>
@@ -441,29 +436,29 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s" s="2">
         <v>32</v>
       </c>
-      <c r="B2" t="s" s="2">
+      <c r="C2" t="s" s="2">
         <v>33</v>
-      </c>
-      <c r="C2" t="s" s="2">
-        <v>34</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -482,32 +477,32 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
